--- a/artfynd/A 60828-2023 artfynd.xlsx
+++ b/artfynd/A 60828-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60828-2023 artfynd.xlsx
+++ b/artfynd/A 60828-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113557418</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113557420</v>
+        <v>113557419</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509547</v>
+        <v>509563</v>
       </c>
       <c r="R3" t="n">
-        <v>7107332</v>
+        <v>7107330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113557419</v>
+        <v>113557420</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509563</v>
+        <v>509547</v>
       </c>
       <c r="R4" t="n">
-        <v>7107330</v>
+        <v>7107332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,12 +984,7 @@
         <v>113557421</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,6 +1080,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122507125</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Myrsnipmyrarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>509687</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7107334</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60828-2023 artfynd.xlsx
+++ b/artfynd/A 60828-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557418</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557419</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557420</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557421</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>